--- a/DownloadedExcels/Distributor.xlsx
+++ b/DownloadedExcels/Distributor.xlsx
@@ -65,7 +65,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -108,32 +108,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C0100001991</t>
+          <t>C0000026863</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A REHMAN G/S</t>
+          <t>Rim Store</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kot Addu Sub DT</t>
+          <t>DEWANHAT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mohalla General Store</t>
+          <t>Urban Neighborhood Grocer</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KARACHI</t>
+          <t/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hiba</t>
+          <t>Joy</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -145,22 +145,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C0100002014</t>
+          <t>C0000026861</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABBASI BROTHERS</t>
+          <t>Kasem Store</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kot Addu Sub DT</t>
+          <t>DEWANHAT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mohalla General Store</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -170,7 +170,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Kasem</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -182,22 +182,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C0124183241</t>
+          <t>C0000026853</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TT Traders</t>
+          <t>Ahamed Telecom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>f008</t>
+          <t>DEWANHAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mohalla General Store</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -207,7 +207,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>Pear Ahamed</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -219,22 +219,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C0124183249</t>
+          <t>C0000026857</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nasim Tahir Stores</t>
+          <t>M Arafat Store</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>f008</t>
+          <t>DEWANHAT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mohalla General Store</t>
+          <t>Urban Neighborhood Grocer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -244,10 +244,3192 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>Md. Hasan Tarek</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C0000026868</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barsha Bitan new</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Shoping Complex/Cosmetic Shop</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>বক্কর স্টোর</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C0000023736</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sujit Store</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MrSujit</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C0000026904</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Outlet Long Name - BD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MA Road</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C0000029547</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Test_9901</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C0000029601</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Outlet_BG_044</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C0012345716</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4-08test</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>123123</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C0012345718</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TEST_02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C0000026906</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Outlet Profile 02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C0012345757</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>smoke testing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>asd</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C0012345765</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JAck</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>21w2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C0012345785</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>uzair1234</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C0000025479</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mahi STORE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Md.Jamal</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C0000025482</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Humayan Store</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Md.Humayan</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C0000023668</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Liaqat Store</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Urban General Store</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>লিয়াকত স্টোর</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C0000025483</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mahin Brothers</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>শাহজালাল সুপার স্টোর</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C0000025485</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Saki Enterprise (C01-2722)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Md.Nurul Kabir</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C0000025486</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M/s. Shahabuddin Enterprise (C01-4260)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Md.Sahabuddin</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C0012346666</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TEST_144</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C0000023667</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Shahjalal Super Store</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TRADITIONAL TRADE BEAUTY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Chwak Bazar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>শাহজালাল সুপার স্টোর</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C0000023760</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JANATA Store</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Babul Dey</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C0000024121</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Yasin Store</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MdJafar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C0000024136</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Allardan Store</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MdSayedul Nabi</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C0000024640</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ma Amena Store</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MdHannan</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C0000024692</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Belal Store</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Belal</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C0000024875</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kader Store</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Md Hasan</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C0000024950</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Family Shop</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MdNasir</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C0000025026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kabir Store</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tayab  Sawdagar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C0000025189</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MA Enterprise</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C0000025346</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Noor Store</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Noor Hassain</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C0000025373</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Delwar Store</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MdDelowar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C0000025398</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>R.S Store new</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Shoping Complex/Cosmetic Shop</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>শরীফ স্টোর</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C0000025403</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chowdhury Store</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>MdMalak</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C0000026018</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>B.M. Store</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Armanul Haque</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C0000026019</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nihad Store</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Md. Ismail</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C0000026143</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Majed Store</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Md. Nurul Amin</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C0000026145</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Al Modina Super Shop</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Md. Alauddin</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C0000026295</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ma Super Shop</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Md. Shahidul Hoque</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C0000026297</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Khandokar Store</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nazrul Islam</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C0000026433</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Saha Azmir Dep</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Towhidul Alam</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C0000026436</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sadia Store 2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Md. Syed</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C0000026582</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tanisa Store</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fatema Begom</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C0000026855</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Delwar Store 2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Delwar</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C0000026858</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tripodi Vander</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Anna Das Gupta</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C0000026859</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>M Rahman Store</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nurul Haque</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C0000026862</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hoque Telecom</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Naimul Haque</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C0000026865</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nizam Cosmetics new</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Shoping Complex/Cosmetic Shop</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>লিয়াকত স্টোর</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C0000026866</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Razia Store</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Salimuddin</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C0000026869</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ktr Store</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Abdul Karim</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C0000026870</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Jobaida  Cosmetics &amp; Store new</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Shoping Complex/Cosmetic Shop</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>শাহজালাল সুপার স্টোর</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C0000026871</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Majumdar Store</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Jewel Majumdar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C0000026872</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Jobaida Store</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Muktar</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C0000026883</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Fruit Bitan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FOOD STORE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Razon</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C0000026884</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Khaza  Fruit Bitan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>FOOD STORE</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Babul</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C0000026885</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Al Habib Fal Bitan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FOOD STORE</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fayez</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C0000026907</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Outlet Profile 03 - BD</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C0000026908</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Outlet Profile 04 - BD</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C0000029591</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Outlet_BG</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C0000029591</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Outlet_BG</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C0012345720</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>TEST_03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C0012345721</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TEST_04</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>C0012345722</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TEST_03</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>C0012345723</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TEST_04</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C0012345724</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TEST_03</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C0012345735</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TEST_14</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C0012345738</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>OutletProfile_BG2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C0012345739</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TEST_144</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C0012345742</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TEST_144</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C0012345744</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TEST_5_6</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C0012345751</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Outlet 007</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>48 Rocky Oak Boulevard B60 4BD</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C0012345758</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Farhan Outlet</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>St1111</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C0012345763</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Jamal Outlet</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>At1232</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C0012345787</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>todayOutletbangla</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C0012345788</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>newoutlet123</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C0012345789</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>newoutlet321</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C0012345790</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>trewoutlet123</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C0000023700</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hasan Store</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Urban General Store</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MdHasan</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C0000023709</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ahmed Store</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>MdJahed Hossain</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C0000024233</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Al Amin Store</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Urban Neighborhood Grocer</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Nurul Abser</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C0000029592</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Outlet_BG</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C0000029593</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Outlet_BG</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>C0000029595</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Outlet_BG01</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C0000029596</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Outlet_bg01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C0000029597</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Outlet_bg01</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>C0000029598</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Outlet_bg01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>C0000029599</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Outlet_bg02</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>C0000029600</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Outlet_bg03</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>DEWANHAT</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Urban Wet Market Grocer</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t/>
         </is>
